--- a/Excel_Data/PD220/XF Real-Time ATP Rate Assay PD220, LV, Healthy 01.09.26 with-XF ATP Rate Assay-ATP Production (Basal Rates) (2).xlsx
+++ b/Excel_Data/PD220/XF Real-Time ATP Rate Assay PD220, LV, Healthy 01.09.26 with-XF ATP Rate Assay-ATP Production (Basal Rates) (2).xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leonardharris/PycharmProjects/FA_Metabolism/Excel_Data/PD220/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBB9DC8-5DA0-954A-8AE7-B48308923205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="1000" windowWidth="15000" windowHeight="10000"/>
+    <workbookView xWindow="-37540" yWindow="7300" windowWidth="15000" windowHeight="10000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ATP Production (Basal Rates)" sheetId="1" r:id="rId1"/>
@@ -139,27 +145,27 @@
     <t>glycoATP Production Rate</t>
   </si>
   <si>
-    <t>XF Real-Time ATP Rate Assay PD220, LV, Healthy 1.9.26 with</t>
+    <t>XF Real-Time ATP Rate Assay PD220, LV, Healthy 01.09.26 with</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -172,7 +178,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border outline="0">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -183,13 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" relativeIndent="0" readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -197,6 +202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -484,380 +497,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="28.5" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
-        <v>10.8734503208764</v>
-      </c>
-      <c r="D10" s="3">
-        <v>10.0208274819702</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="C10" s="2">
+        <v>10.873450320876399</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10.020827481970199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
-        <v>6.6067619701545</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="2">
+        <v>6.6067619701545004</v>
+      </c>
+      <c r="D11" s="2">
         <v>13.2795424461063</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>7.59466277935298</v>
       </c>
-      <c r="D12" s="3">
-        <v>14.9172321912185</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="D12" s="2">
+        <v>14.917232191218501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="3">
-        <v>8.88239900524825</v>
-      </c>
-      <c r="D13" s="3">
-        <v>15.4101725993743</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="C13" s="2">
+        <v>8.8823990052482493</v>
+      </c>
+      <c r="D13" s="2">
+        <v>15.410172599374301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3">
-        <v>6.93858644026708</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="2">
+        <v>6.9385864402670796</v>
+      </c>
+      <c r="D14" s="2">
         <v>16.1437528608046</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3">
-        <v>8.81749544853426</v>
-      </c>
-      <c r="D15" s="3">
-        <v>12.5875184656521</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="C15" s="2">
+        <v>8.8174954485342596</v>
+      </c>
+      <c r="D15" s="2">
+        <v>12.587518465652099</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="3">
-        <v>3.77385974949443</v>
-      </c>
-      <c r="D16" s="3">
-        <v>7.09021233960073</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="C16" s="2">
+        <v>3.7738597494944299</v>
+      </c>
+      <c r="D16" s="2">
+        <v>7.0902123396007299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="3">
-        <v>4.63483217726423</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="C17" s="2">
+        <v>4.6348321772642302</v>
+      </c>
+      <c r="D17" s="2">
         <v>10.8518595686746</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>5.00370852308557</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>12.6198943220387</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="3">
-        <v>4.6494836843968</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="C19" s="2">
+        <v>4.6494836843967997</v>
+      </c>
+      <c r="D19" s="2">
         <v>7.83062713099583</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3">
-        <v>6.17681464819178</v>
-      </c>
-      <c r="D20" s="3">
-        <v>10.0139071209929</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="C20" s="2">
+        <v>6.1768146481917796</v>
+      </c>
+      <c r="D20" s="2">
+        <v>10.013907120992901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="3">
-        <v>4.5113777876521</v>
-      </c>
-      <c r="D21" s="3">
-        <v>8.97782310149629</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="C21" s="2">
+        <v>4.5113777876521004</v>
+      </c>
+      <c r="D21" s="2">
+        <v>8.9778231014962895</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="3">
-        <v>5.02608236126307</v>
-      </c>
-      <c r="D22" s="3">
-        <v>8.18071461838454</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="C22" s="2">
+        <v>5.0260823612630698</v>
+      </c>
+      <c r="D22" s="2">
+        <v>8.1807146183845401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="3">
-        <v>3.8066316943892</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="C23" s="2">
+        <v>3.8066316943891998</v>
+      </c>
+      <c r="D23" s="2">
         <v>22.6409003531517</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
-        <v>6.09403486451189</v>
-      </c>
-      <c r="D24" s="3">
-        <v>26.6350472466674</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="C24" s="2">
+        <v>6.0940348645118902</v>
+      </c>
+      <c r="D24" s="2">
+        <v>26.635047246667401</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="3">
-        <v>4.52927725486529</v>
-      </c>
-      <c r="D25" s="3">
-        <v>23.0341641615845</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="C25" s="2">
+        <v>4.5292772548652902</v>
+      </c>
+      <c r="D25" s="2">
+        <v>23.034164161584499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="3">
-        <v>5.05003317647038</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="C26" s="2">
+        <v>5.0500331764703796</v>
+      </c>
+      <c r="D26" s="2">
         <v>23.3426949888655</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="3">
-        <v>6.21403085614764</v>
-      </c>
-      <c r="D27" s="3">
-        <v>22.0659343659278</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="C27" s="2">
+        <v>6.2140308561476401</v>
+      </c>
+      <c r="D27" s="2">
+        <v>22.065934365927799</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="3">
-        <v>3.60381325231249</v>
-      </c>
-      <c r="D28" s="3">
-        <v>23.7817819501532</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
+      <c r="C28" s="2">
+        <v>3.6038132523124902</v>
+      </c>
+      <c r="D28" s="2">
+        <v>23.781781950153199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="3">
-        <v>3.32519834259744</v>
-      </c>
-      <c r="D29" s="3">
-        <v>22.0959331900629</v>
+      <c r="C29" s="2">
+        <v>3.3251983425974401</v>
+      </c>
+      <c r="D29" s="2">
+        <v>22.095933190062901</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection/>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>